--- a/knockout_schedule.xlsx
+++ b/knockout_schedule.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wanj\Desktop\worldcup-betting\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FBB7908-EE99-4ABA-8D1E-A641040C1E67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C5B0A16-4232-421F-A1BF-31583FB02A97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{C09E0143-236E-47C5-9D28-849AD855BD11}"/>
+    <workbookView xWindow="-108" yWindow="-13068" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{C09E0143-236E-47C5-9D28-849AD855BD11}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId2"/>
-    <sheet name="Sheet2" sheetId="4" r:id="rId3"/>
+    <sheet name="Sheet4" sheetId="5" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet2" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="158">
   <si>
     <t>round_name</t>
   </si>
@@ -377,6 +378,144 @@
   </si>
   <si>
     <t>ishomeinnext</t>
+  </si>
+  <si>
+    <t>Round</t>
+  </si>
+  <si>
+    <t>Match</t>
+  </si>
+  <si>
+    <t>Team1</t>
+  </si>
+  <si>
+    <t>Team2</t>
+  </si>
+  <si>
+    <t>Score</t>
+  </si>
+  <si>
+    <t>Winner</t>
+  </si>
+  <si>
+    <t>Next ID</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Bosn. &amp; Herz.</t>
+  </si>
+  <si>
+    <t>Argentina</t>
+  </si>
+  <si>
+    <t>Knockout Debug View</t>
+  </si>
+  <si>
+    <t>Czech Rep.</t>
+  </si>
+  <si>
+    <t>Belgium</t>
+  </si>
+  <si>
+    <t>Brazil</t>
+  </si>
+  <si>
+    <t>France</t>
+  </si>
+  <si>
+    <t>Egypt</t>
+  </si>
+  <si>
+    <t>Mexico</t>
+  </si>
+  <si>
+    <t>South Africa</t>
+  </si>
+  <si>
+    <t>Rep. of Korea</t>
+  </si>
+  <si>
+    <t>Canada</t>
+  </si>
+  <si>
+    <t>USA</t>
+  </si>
+  <si>
+    <t>Paraguay</t>
+  </si>
+  <si>
+    <t>Morocco</t>
+  </si>
+  <si>
+    <t>Qatar</t>
+  </si>
+  <si>
+    <t>Switzerland</t>
+  </si>
+  <si>
+    <t>Haiti</t>
+  </si>
+  <si>
+    <t>Scotland</t>
+  </si>
+  <si>
+    <t>Australia</t>
+  </si>
+  <si>
+    <t>Turkey</t>
+  </si>
+  <si>
+    <t>Netherlands</t>
+  </si>
+  <si>
+    <t>Japan</t>
+  </si>
+  <si>
+    <t>Ivory Coast</t>
+  </si>
+  <si>
+    <t>Ecuador</t>
+  </si>
+  <si>
+    <t>Sweden</t>
+  </si>
+  <si>
+    <t>Tunisia</t>
+  </si>
+  <si>
+    <t>Spain</t>
+  </si>
+  <si>
+    <t>Cape Verde</t>
+  </si>
+  <si>
+    <t>Saudi Arabia</t>
+  </si>
+  <si>
+    <t>Uruguay</t>
+  </si>
+  <si>
+    <t>IR Iran</t>
+  </si>
+  <si>
+    <t>New Zealand</t>
+  </si>
+  <si>
+    <t>Senegal</t>
+  </si>
+  <si>
+    <t>update knockout_match set team1 = '</t>
+  </si>
+  <si>
+    <t>;</t>
+  </si>
+  <si>
+    <t>', team2 ='</t>
+  </si>
+  <si>
+    <t xml:space="preserve">' where match_number = </t>
   </si>
 </sst>
 </file>
@@ -414,9 +553,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1382,7 +1523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>12</v>
       </c>
@@ -1422,6 +1563,457 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{523F9CB6-A07B-4313-A0FF-04AEC136526D}">
+  <dimension ref="A1:H16"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="31.09765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="2.8984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="1.3984375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="F1">
+        <v>74</v>
+      </c>
+      <c r="G1" t="s">
+        <v>155</v>
+      </c>
+      <c r="H1" t="str">
+        <f>_xlfn.CONCAT(A1:G1)</f>
+        <v>update knockout_match set team1 = 'Mexico', team2 ='Netherlands' where match_number = 74;</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="F2">
+        <v>77</v>
+      </c>
+      <c r="G2" t="s">
+        <v>155</v>
+      </c>
+      <c r="H2" t="str">
+        <f t="shared" ref="H2:H48" si="0">_xlfn.CONCAT(A2:G2)</f>
+        <v>update knockout_match set team1 = 'South Africa', team2 ='Japan' where match_number = 77;</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D3" t="s">
+        <v>143</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="F3">
+        <v>73</v>
+      </c>
+      <c r="G3" t="s">
+        <v>155</v>
+      </c>
+      <c r="H3" t="str">
+        <f t="shared" si="0"/>
+        <v>update knockout_match set team1 = 'Rep. of Korea', team2 ='Ivory Coast' where match_number = 73;</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>154</v>
+      </c>
+      <c r="B4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D4" t="s">
+        <v>144</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="F4">
+        <v>75</v>
+      </c>
+      <c r="G4" t="s">
+        <v>155</v>
+      </c>
+      <c r="H4" t="str">
+        <f t="shared" si="0"/>
+        <v>update knockout_match set team1 = 'Czech Rep.', team2 ='Ecuador' where match_number = 75;</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>154</v>
+      </c>
+      <c r="B5" t="s">
+        <v>131</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D5" t="s">
+        <v>145</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="F5">
+        <v>83</v>
+      </c>
+      <c r="G5" t="s">
+        <v>155</v>
+      </c>
+      <c r="H5" t="str">
+        <f t="shared" si="0"/>
+        <v>update knockout_match set team1 = 'Canada', team2 ='Sweden' where match_number = 83;</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>154</v>
+      </c>
+      <c r="B6" t="s">
+        <v>120</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D6" t="s">
+        <v>146</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="F6">
+        <v>84</v>
+      </c>
+      <c r="G6" t="s">
+        <v>155</v>
+      </c>
+      <c r="H6" t="str">
+        <f t="shared" si="0"/>
+        <v>update knockout_match set team1 = 'Bosn. &amp; Herz.', team2 ='Tunisia' where match_number = 84;</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>154</v>
+      </c>
+      <c r="B7" t="s">
+        <v>132</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D7" t="s">
+        <v>147</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="F7">
+        <v>81</v>
+      </c>
+      <c r="G7" t="s">
+        <v>155</v>
+      </c>
+      <c r="H7" t="str">
+        <f t="shared" si="0"/>
+        <v>update knockout_match set team1 = 'USA', team2 ='Spain' where match_number = 81;</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>154</v>
+      </c>
+      <c r="B8" t="s">
+        <v>133</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D8" t="s">
+        <v>148</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="F8">
+        <v>82</v>
+      </c>
+      <c r="G8" t="s">
+        <v>155</v>
+      </c>
+      <c r="H8" t="str">
+        <f t="shared" si="0"/>
+        <v>update knockout_match set team1 = 'Paraguay', team2 ='Cape Verde' where match_number = 82;</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>154</v>
+      </c>
+      <c r="B9" t="s">
+        <v>125</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D9" t="s">
+        <v>124</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="F9">
+        <v>76</v>
+      </c>
+      <c r="G9" t="s">
+        <v>155</v>
+      </c>
+      <c r="H9" t="str">
+        <f t="shared" si="0"/>
+        <v>update knockout_match set team1 = 'Brazil', team2 ='Belgium' where match_number = 76;</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>154</v>
+      </c>
+      <c r="B10" t="s">
+        <v>134</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D10" t="s">
+        <v>127</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="F10">
+        <v>78</v>
+      </c>
+      <c r="G10" t="s">
+        <v>155</v>
+      </c>
+      <c r="H10" t="str">
+        <f t="shared" si="0"/>
+        <v>update knockout_match set team1 = 'Morocco', team2 ='Egypt' where match_number = 78;</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>154</v>
+      </c>
+      <c r="B11" t="s">
+        <v>135</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D11" t="s">
+        <v>149</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="F11">
+        <v>79</v>
+      </c>
+      <c r="G11" t="s">
+        <v>155</v>
+      </c>
+      <c r="H11" t="str">
+        <f t="shared" si="0"/>
+        <v>update knockout_match set team1 = 'Qatar', team2 ='Saudi Arabia' where match_number = 79;</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>154</v>
+      </c>
+      <c r="B12" t="s">
+        <v>136</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D12" t="s">
+        <v>150</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="F12">
+        <v>80</v>
+      </c>
+      <c r="G12" t="s">
+        <v>155</v>
+      </c>
+      <c r="H12" t="str">
+        <f t="shared" si="0"/>
+        <v>update knockout_match set team1 = 'Switzerland', team2 ='Uruguay' where match_number = 80;</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>154</v>
+      </c>
+      <c r="B13" t="s">
+        <v>137</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D13" t="s">
+        <v>151</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="F13">
+        <v>86</v>
+      </c>
+      <c r="G13" t="s">
+        <v>155</v>
+      </c>
+      <c r="H13" t="str">
+        <f t="shared" si="0"/>
+        <v>update knockout_match set team1 = 'Haiti', team2 ='IR Iran' where match_number = 86;</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>154</v>
+      </c>
+      <c r="B14" t="s">
+        <v>138</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D14" t="s">
+        <v>152</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="F14">
+        <v>88</v>
+      </c>
+      <c r="G14" t="s">
+        <v>155</v>
+      </c>
+      <c r="H14" t="str">
+        <f t="shared" si="0"/>
+        <v>update knockout_match set team1 = 'Scotland', team2 ='New Zealand' where match_number = 88;</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>154</v>
+      </c>
+      <c r="B15" t="s">
+        <v>139</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D15" t="s">
+        <v>126</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="F15">
+        <v>85</v>
+      </c>
+      <c r="G15" t="s">
+        <v>155</v>
+      </c>
+      <c r="H15" t="str">
+        <f t="shared" si="0"/>
+        <v>update knockout_match set team1 = 'Australia', team2 ='France' where match_number = 85;</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>154</v>
+      </c>
+      <c r="B16" t="s">
+        <v>140</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D16" t="s">
+        <v>153</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="F16">
+        <v>87</v>
+      </c>
+      <c r="G16" t="s">
+        <v>155</v>
+      </c>
+      <c r="H16" t="str">
+        <f t="shared" si="0"/>
+        <v>update knockout_match set team1 = 'Turkey', team2 ='Senegal' where match_number = 87;</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3798C30F-2D18-4B4F-A637-6433A109E055}">
   <dimension ref="A1:C17"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
@@ -1623,112 +2215,840 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10D4A4FD-15FE-4E86-B306-CDCF953C4DBD}">
-  <dimension ref="A1:A20"/>
+  <dimension ref="A1:K36"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.69921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="E2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="E4" t="s">
+        <v>112</v>
+      </c>
+      <c r="F4" t="s">
+        <v>113</v>
+      </c>
+      <c r="G4" t="s">
+        <v>114</v>
+      </c>
+      <c r="H4" t="s">
+        <v>115</v>
+      </c>
+      <c r="I4" t="s">
+        <v>116</v>
+      </c>
+      <c r="J4" t="s">
+        <v>117</v>
+      </c>
+      <c r="K4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="E5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5">
+        <v>104</v>
+      </c>
+      <c r="G5" t="s">
+        <v>119</v>
+      </c>
+      <c r="H5" t="s">
+        <v>119</v>
+      </c>
+      <c r="I5" t="s">
+        <v>119</v>
+      </c>
+      <c r="J5" t="s">
+        <v>119</v>
+      </c>
+      <c r="K5" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="E6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6">
+        <v>97</v>
+      </c>
+      <c r="G6" t="s">
+        <v>119</v>
+      </c>
+      <c r="H6" t="s">
+        <v>119</v>
+      </c>
+      <c r="I6" t="s">
+        <v>119</v>
+      </c>
+      <c r="J6" t="s">
+        <v>119</v>
+      </c>
+      <c r="K6">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="E7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7">
+        <v>98</v>
+      </c>
+      <c r="G7" t="s">
+        <v>119</v>
+      </c>
+      <c r="H7" t="s">
+        <v>119</v>
+      </c>
+      <c r="I7" t="s">
+        <v>119</v>
+      </c>
+      <c r="J7" t="s">
+        <v>119</v>
+      </c>
+      <c r="K7">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="E8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8">
+        <v>99</v>
+      </c>
+      <c r="G8" t="s">
+        <v>119</v>
+      </c>
+      <c r="H8" t="s">
+        <v>119</v>
+      </c>
+      <c r="I8" t="s">
+        <v>119</v>
+      </c>
+      <c r="J8" t="s">
+        <v>119</v>
+      </c>
+      <c r="K8">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="E9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9">
+        <v>100</v>
+      </c>
+      <c r="G9" t="s">
+        <v>119</v>
+      </c>
+      <c r="H9" t="s">
+        <v>119</v>
+      </c>
+      <c r="I9" t="s">
+        <v>119</v>
+      </c>
+      <c r="J9" t="s">
+        <v>119</v>
+      </c>
+      <c r="K9">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="E10" t="s">
+        <v>61</v>
+      </c>
+      <c r="F10">
+        <v>89</v>
+      </c>
+      <c r="G10" t="s">
+        <v>119</v>
+      </c>
+      <c r="H10" t="s">
+        <v>119</v>
+      </c>
+      <c r="I10" t="s">
+        <v>119</v>
+      </c>
+      <c r="J10" t="s">
+        <v>119</v>
+      </c>
+      <c r="K10">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="E11" t="s">
+        <v>61</v>
+      </c>
+      <c r="F11">
+        <v>90</v>
+      </c>
+      <c r="G11" t="s">
+        <v>121</v>
+      </c>
+      <c r="H11" t="s">
+        <v>126</v>
+      </c>
+      <c r="I11" t="s">
+        <v>119</v>
+      </c>
+      <c r="J11" t="s">
+        <v>119</v>
+      </c>
+      <c r="K11">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="E12" t="s">
+        <v>61</v>
+      </c>
+      <c r="F12">
+        <v>91</v>
+      </c>
+      <c r="G12" t="s">
+        <v>119</v>
+      </c>
+      <c r="H12" t="s">
+        <v>119</v>
+      </c>
+      <c r="I12" t="s">
+        <v>119</v>
+      </c>
+      <c r="J12" t="s">
+        <v>119</v>
+      </c>
+      <c r="K12">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="E13" t="s">
+        <v>61</v>
+      </c>
+      <c r="F13">
+        <v>92</v>
+      </c>
+      <c r="G13" t="s">
+        <v>119</v>
+      </c>
+      <c r="H13" t="s">
+        <v>119</v>
+      </c>
+      <c r="I13" t="s">
+        <v>119</v>
+      </c>
+      <c r="J13" t="s">
+        <v>119</v>
+      </c>
+      <c r="K13">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="E14" t="s">
+        <v>61</v>
+      </c>
+      <c r="F14">
+        <v>93</v>
+      </c>
+      <c r="G14" t="s">
+        <v>119</v>
+      </c>
+      <c r="H14" t="s">
+        <v>119</v>
+      </c>
+      <c r="I14" t="s">
+        <v>119</v>
+      </c>
+      <c r="J14" t="s">
+        <v>119</v>
+      </c>
+      <c r="K14">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="E15" t="s">
+        <v>61</v>
+      </c>
+      <c r="F15">
+        <v>94</v>
+      </c>
+      <c r="G15" t="s">
+        <v>119</v>
+      </c>
+      <c r="H15" t="s">
+        <v>119</v>
+      </c>
+      <c r="I15" t="s">
+        <v>119</v>
+      </c>
+      <c r="J15" t="s">
+        <v>119</v>
+      </c>
+      <c r="K15">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="E16" t="s">
+        <v>61</v>
+      </c>
+      <c r="F16">
+        <v>95</v>
+      </c>
+      <c r="G16" t="s">
+        <v>119</v>
+      </c>
+      <c r="H16" t="s">
+        <v>119</v>
+      </c>
+      <c r="I16" t="s">
+        <v>119</v>
+      </c>
+      <c r="J16" t="s">
+        <v>119</v>
+      </c>
+      <c r="K16">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="E17" t="s">
+        <v>61</v>
+      </c>
+      <c r="F17">
+        <v>96</v>
+      </c>
+      <c r="G17" t="s">
+        <v>119</v>
+      </c>
+      <c r="H17" t="s">
+        <v>119</v>
+      </c>
+      <c r="I17" t="s">
+        <v>119</v>
+      </c>
+      <c r="J17" t="s">
+        <v>119</v>
+      </c>
+      <c r="K17">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="E18" t="s">
+        <v>60</v>
+      </c>
+      <c r="F18">
+        <v>73</v>
+      </c>
+      <c r="G18" t="s">
+        <v>120</v>
+      </c>
+      <c r="H18" t="s">
+        <v>121</v>
+      </c>
+      <c r="I18" s="2">
+        <v>46024</v>
+      </c>
+      <c r="J18" t="s">
+        <v>121</v>
+      </c>
+      <c r="K18">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="E19" t="s">
+        <v>60</v>
+      </c>
+      <c r="F19">
+        <v>74</v>
+      </c>
+      <c r="G19" t="s">
+        <v>119</v>
+      </c>
+      <c r="H19" t="s">
+        <v>119</v>
+      </c>
+      <c r="I19" t="s">
+        <v>119</v>
+      </c>
+      <c r="J19" t="s">
+        <v>119</v>
+      </c>
+      <c r="K19">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>111</v>
+      </c>
+      <c r="E20" t="s">
+        <v>60</v>
+      </c>
+      <c r="F20">
+        <v>75</v>
+      </c>
+      <c r="G20" t="s">
+        <v>126</v>
+      </c>
+      <c r="H20" t="s">
+        <v>127</v>
+      </c>
+      <c r="I20" t="s">
+        <v>119</v>
+      </c>
+      <c r="J20" t="s">
+        <v>119</v>
+      </c>
+      <c r="K20">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E21" t="s">
+        <v>60</v>
+      </c>
+      <c r="F21">
+        <v>76</v>
+      </c>
+      <c r="G21" t="s">
+        <v>119</v>
+      </c>
+      <c r="H21" t="s">
+        <v>119</v>
+      </c>
+      <c r="I21" t="s">
+        <v>119</v>
+      </c>
+      <c r="J21" t="s">
+        <v>119</v>
+      </c>
+      <c r="K21">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E22" t="s">
+        <v>60</v>
+      </c>
+      <c r="F22">
+        <v>77</v>
+      </c>
+      <c r="G22" t="s">
+        <v>119</v>
+      </c>
+      <c r="H22" t="s">
+        <v>119</v>
+      </c>
+      <c r="I22" t="s">
+        <v>119</v>
+      </c>
+      <c r="J22" t="s">
+        <v>119</v>
+      </c>
+      <c r="K22">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E23" t="s">
+        <v>60</v>
+      </c>
+      <c r="F23">
+        <v>78</v>
+      </c>
+      <c r="G23" t="s">
+        <v>119</v>
+      </c>
+      <c r="H23" t="s">
+        <v>119</v>
+      </c>
+      <c r="I23" t="s">
+        <v>119</v>
+      </c>
+      <c r="J23" t="s">
+        <v>119</v>
+      </c>
+      <c r="K23">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E24" t="s">
+        <v>60</v>
+      </c>
+      <c r="F24">
+        <v>79</v>
+      </c>
+      <c r="G24" t="s">
+        <v>119</v>
+      </c>
+      <c r="H24" t="s">
+        <v>119</v>
+      </c>
+      <c r="I24" t="s">
+        <v>119</v>
+      </c>
+      <c r="J24" t="s">
+        <v>119</v>
+      </c>
+      <c r="K24">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E25" t="s">
+        <v>60</v>
+      </c>
+      <c r="F25">
+        <v>80</v>
+      </c>
+      <c r="G25" t="s">
+        <v>119</v>
+      </c>
+      <c r="H25" t="s">
+        <v>119</v>
+      </c>
+      <c r="I25" t="s">
+        <v>119</v>
+      </c>
+      <c r="J25" t="s">
+        <v>119</v>
+      </c>
+      <c r="K25">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E26" t="s">
+        <v>60</v>
+      </c>
+      <c r="F26">
+        <v>81</v>
+      </c>
+      <c r="G26" t="s">
+        <v>119</v>
+      </c>
+      <c r="H26" t="s">
+        <v>119</v>
+      </c>
+      <c r="I26" t="s">
+        <v>119</v>
+      </c>
+      <c r="J26" t="s">
+        <v>119</v>
+      </c>
+      <c r="K26">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E27" t="s">
+        <v>60</v>
+      </c>
+      <c r="F27">
+        <v>82</v>
+      </c>
+      <c r="G27" t="s">
+        <v>119</v>
+      </c>
+      <c r="H27" t="s">
+        <v>119</v>
+      </c>
+      <c r="I27" t="s">
+        <v>119</v>
+      </c>
+      <c r="J27" t="s">
+        <v>119</v>
+      </c>
+      <c r="K27">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E28" t="s">
+        <v>60</v>
+      </c>
+      <c r="F28">
+        <v>83</v>
+      </c>
+      <c r="G28" t="s">
+        <v>119</v>
+      </c>
+      <c r="H28" t="s">
+        <v>119</v>
+      </c>
+      <c r="I28" t="s">
+        <v>119</v>
+      </c>
+      <c r="J28" t="s">
+        <v>119</v>
+      </c>
+      <c r="K28">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E29" t="s">
+        <v>60</v>
+      </c>
+      <c r="F29">
+        <v>84</v>
+      </c>
+      <c r="G29" t="s">
+        <v>119</v>
+      </c>
+      <c r="H29" t="s">
+        <v>119</v>
+      </c>
+      <c r="I29" t="s">
+        <v>119</v>
+      </c>
+      <c r="J29" t="s">
+        <v>119</v>
+      </c>
+      <c r="K29">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E30" t="s">
+        <v>60</v>
+      </c>
+      <c r="F30">
+        <v>85</v>
+      </c>
+      <c r="G30" t="s">
+        <v>119</v>
+      </c>
+      <c r="H30" t="s">
+        <v>119</v>
+      </c>
+      <c r="I30" t="s">
+        <v>119</v>
+      </c>
+      <c r="J30" t="s">
+        <v>119</v>
+      </c>
+      <c r="K30">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E31" t="s">
+        <v>60</v>
+      </c>
+      <c r="F31">
+        <v>86</v>
+      </c>
+      <c r="G31" t="s">
+        <v>119</v>
+      </c>
+      <c r="H31" t="s">
+        <v>119</v>
+      </c>
+      <c r="I31" t="s">
+        <v>119</v>
+      </c>
+      <c r="J31" t="s">
+        <v>119</v>
+      </c>
+      <c r="K31">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E32" t="s">
+        <v>60</v>
+      </c>
+      <c r="F32">
+        <v>87</v>
+      </c>
+      <c r="G32" t="s">
+        <v>119</v>
+      </c>
+      <c r="H32" t="s">
+        <v>119</v>
+      </c>
+      <c r="I32" t="s">
+        <v>119</v>
+      </c>
+      <c r="J32" t="s">
+        <v>119</v>
+      </c>
+      <c r="K32">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="33" spans="5:11" x14ac:dyDescent="0.25">
+      <c r="E33" t="s">
+        <v>60</v>
+      </c>
+      <c r="F33">
+        <v>88</v>
+      </c>
+      <c r="G33" t="s">
+        <v>119</v>
+      </c>
+      <c r="H33" t="s">
+        <v>119</v>
+      </c>
+      <c r="I33" t="s">
+        <v>119</v>
+      </c>
+      <c r="J33" t="s">
+        <v>119</v>
+      </c>
+      <c r="K33">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="34" spans="5:11" x14ac:dyDescent="0.25">
+      <c r="E34" t="s">
+        <v>11</v>
+      </c>
+      <c r="F34">
+        <v>101</v>
+      </c>
+      <c r="G34" t="s">
+        <v>119</v>
+      </c>
+      <c r="H34" t="s">
+        <v>119</v>
+      </c>
+      <c r="I34" t="s">
+        <v>119</v>
+      </c>
+      <c r="J34" t="s">
+        <v>119</v>
+      </c>
+      <c r="K34">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="35" spans="5:11" x14ac:dyDescent="0.25">
+      <c r="E35" t="s">
+        <v>11</v>
+      </c>
+      <c r="F35">
+        <v>102</v>
+      </c>
+      <c r="G35" t="s">
+        <v>119</v>
+      </c>
+      <c r="H35" t="s">
+        <v>119</v>
+      </c>
+      <c r="I35" t="s">
+        <v>119</v>
+      </c>
+      <c r="J35" t="s">
+        <v>119</v>
+      </c>
+      <c r="K35">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="36" spans="5:11" x14ac:dyDescent="0.25">
+      <c r="E36" t="s">
+        <v>12</v>
+      </c>
+      <c r="F36">
+        <v>103</v>
+      </c>
+      <c r="G36" t="s">
+        <v>119</v>
+      </c>
+      <c r="H36" t="s">
+        <v>119</v>
+      </c>
+      <c r="I36" t="s">
+        <v>119</v>
+      </c>
+      <c r="J36" t="s">
+        <v>119</v>
+      </c>
+      <c r="K36" t="s">
+        <v>119</v>
       </c>
     </row>
   </sheetData>

--- a/knockout_schedule.xlsx
+++ b/knockout_schedule.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wanj\Desktop\worldcup-betting\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C5B0A16-4232-421F-A1BF-31583FB02A97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D54DC72-0613-4D22-8684-BFB484DE138C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-13068" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{C09E0143-236E-47C5-9D28-849AD855BD11}"/>
+    <workbookView xWindow="-11616" yWindow="-13092" windowWidth="11712" windowHeight="12336" xr2:uid="{C09E0143-236E-47C5-9D28-849AD855BD11}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet4" sheetId="5" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
     <sheet name="Sheet2" sheetId="4" r:id="rId4"/>
+    <sheet name="Sheet5" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="159">
   <si>
     <t>round_name</t>
   </si>
@@ -516,6 +517,9 @@
   </si>
   <si>
     <t xml:space="preserve">' where match_number = </t>
+  </si>
+  <si>
+    <t>m</t>
   </si>
 </sst>
 </file>
@@ -553,11 +557,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1111,7 +1124,7 @@
         <v>71</v>
       </c>
       <c r="C11" s="1">
-        <v>45839.041666666664</v>
+        <v>46204.041666666664</v>
       </c>
       <c r="D11" t="s">
         <v>51</v>
@@ -1626,7 +1639,7 @@
         <v>155</v>
       </c>
       <c r="H2" t="str">
-        <f t="shared" ref="H2:H48" si="0">_xlfn.CONCAT(A2:G2)</f>
+        <f t="shared" ref="H2:H16" si="0">_xlfn.CONCAT(A2:G2)</f>
         <v>update knockout_match set team1 = 'South Africa', team2 ='Japan' where match_number = 77;</v>
       </c>
     </row>
@@ -3054,4 +3067,237 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6E8676C-4801-4713-A2CC-E722C23FDA8F}">
+  <dimension ref="A1:E27"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="D3" s="5"/>
+      <c r="E3" s="6" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="C4" s="6"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="6"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="B5" s="6"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="E5" s="5"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="C6" s="5"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="5"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="D7" s="5"/>
+      <c r="E7" s="6" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="C8" s="6"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="6"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="B9" s="6"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="4"/>
+      <c r="B13" s="6" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B14" s="6"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="4"/>
+      <c r="C15" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C16" s="6"/>
+      <c r="E16" s="6"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="4"/>
+      <c r="B17" s="6" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B18" s="6"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="4"/>
+      <c r="D19" s="6" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="D20" s="6"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="4"/>
+      <c r="B21" s="6" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B22" s="6"/>
+      <c r="E22" s="6" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="4"/>
+      <c r="C23" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="E23" s="6"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C24" s="6"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="4"/>
+      <c r="B25" s="6" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B26" s="6"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="4"/>
+    </row>
+  </sheetData>
+  <mergeCells count="26">
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="C7:C8"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>